--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B44" s="42" t="inlineStr">
         <is>
-          <t>Heavy pull + press (3 x 5), then short arms block B (lateral raises, cable crunch), then engine EMOM as the finisher (no grip, saves it for Saturday): SkiErg, wall balls, row, burpee broad jumps</t>
+          <t>Heavy pull + press (3 x 5), then short arms block B (face pulls, cable crunch), then engine EMOM as the finisher (no grip, saves it for Saturday): SkiErg, wall balls, row, burpee broad jumps</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       <c r="G2" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
         </is>
       </c>
@@ -1649,7 +1649,7 @@
       <c r="G3" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
         </is>
       </c>
@@ -1701,7 +1701,7 @@
       <c r="G4" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
         </is>
       </c>
@@ -1753,7 +1753,7 @@
       <c r="G5" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Lateral raises 3x15, cable crunch 3x10
+Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
         </is>
       </c>
@@ -1805,7 +1805,7 @@
       <c r="G6" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
         </is>
       </c>
@@ -1857,7 +1857,7 @@
       <c r="G7" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
         </is>
       </c>
@@ -1909,7 +1909,7 @@
       <c r="G8" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
         </is>
       </c>
@@ -1961,7 +1961,7 @@
       <c r="G9" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Lateral raises 3x15, cable crunch 3x10
+Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
         </is>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="G10" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 20 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
         </is>
       </c>
@@ -2069,7 +2069,7 @@
       <c r="G11" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 20 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
         </is>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="G12" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 20 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
         </is>
       </c>
@@ -2173,7 +2173,7 @@
       <c r="G13" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Lateral raises 3x15, cable crunch 3x10
+Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
         </is>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="G14" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 25 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
         </is>
       </c>
@@ -2281,7 +2281,7 @@
       <c r="G15" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 25 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
         </is>
       </c>
@@ -2333,7 +2333,7 @@
       <c r="G16" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="G17" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Lateral raises 3x15, cable crunch 3x10
+Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
         </is>
       </c>
@@ -2441,7 +2441,7 @@
       <c r="G18" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2493,7 +2493,7 @@
       <c r="G19" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="G20" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2601,7 +2601,7 @@
       <c r="G21" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Lateral raises 3x15, cable crunch 3x10
+Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
         </is>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="G22" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="G23" s="49" t="inlineStr">
         <is>
           <t>Pull ups 3 x 5, press 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min at race effort: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2761,7 +2761,7 @@
       <c r="G24" s="49" t="inlineStr">
         <is>
           <t>Pull ups 3 x 5, press 3 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 20 min at race effort: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2813,7 +2813,7 @@
       <c r="G25" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5.
-Then arms block B: Lateral raises 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 8 min light: SkiErg, wall balls, row, rest</t>
         </is>
       </c>
@@ -2869,7 +2869,7 @@
       <c r="G26" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5.
-Then arms block B, 2 sets each: Lateral raises 3x15, cable crunch 3x10
+Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
 Finisher: EMOM 12 min at race effort, short sets</t>
         </is>
       </c>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B42" s="42" t="inlineStr">
         <is>
-          <t>REST (10 min mobility optional: neck, hips)</t>
+          <t>REST + 12 min mobility routine (daily 3 moves: 4 min)</t>
         </is>
       </c>
     </row>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -702,6 +702,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="39">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -801,6 +802,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="39">
       <c r="A12" s="47" t="inlineStr">
         <is>
@@ -822,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="39">
       <c r="A16" s="47" t="inlineStr">
         <is>
@@ -1063,6 +1066,8 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="39">
       <c r="A29" s="47" t="inlineStr">
         <is>
@@ -1259,6 +1264,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="15" customHeight="1" s="39">
       <c r="A38" s="47" t="inlineStr">
         <is>
@@ -1365,6 +1371,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48" ht="15" customHeight="1" s="39">
       <c r="A48" s="47" t="inlineStr">
         <is>
@@ -1592,9 +1599,9 @@
       </c>
       <c r="G2" s="49" t="inlineStr">
         <is>
-          <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
+          <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
+Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H2" s="49" t="inlineStr">
@@ -1648,9 +1655,9 @@
       </c>
       <c r="G3" s="49" t="inlineStr">
         <is>
-          <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
+          <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
+Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H3" s="49" t="inlineStr">
@@ -1700,9 +1707,9 @@
       </c>
       <c r="G4" s="49" t="inlineStr">
         <is>
-          <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
+          <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
+Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H4" s="49" t="inlineStr">
@@ -1754,7 +1761,7 @@
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
 Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
+Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
         </is>
       </c>
       <c r="H5" s="49" t="inlineStr">
@@ -1804,9 +1811,9 @@
       </c>
       <c r="G6" s="49" t="inlineStr">
         <is>
-          <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
+          <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
+Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H6" s="49" t="inlineStr">
@@ -1856,9 +1863,9 @@
       </c>
       <c r="G7" s="49" t="inlineStr">
         <is>
-          <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
+          <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
+Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H7" s="49" t="inlineStr">
@@ -1908,9 +1915,9 @@
       </c>
       <c r="G8" s="49" t="inlineStr">
         <is>
-          <t>Weighted pull ups 3 x 5, DB bench 3 x 5.
+          <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 16 min: 1) SkiErg 12 cal 2) 15 wall balls 3) row 12 cal 4) rest</t>
+Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H8" s="49" t="inlineStr">
@@ -1962,7 +1969,7 @@
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
 Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
+Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
         </is>
       </c>
       <c r="H9" s="49" t="inlineStr">
@@ -2018,7 +2025,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 20 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
+Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
       <c r="H10" s="49" t="inlineStr">
@@ -2070,7 +2077,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 20 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
+Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
       <c r="H11" s="49" t="inlineStr">
@@ -2122,7 +2129,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 20 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
+Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
       <c r="H12" s="49" t="inlineStr">
@@ -2174,7 +2181,7 @@
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
 Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
+Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
         </is>
       </c>
       <c r="H13" s="49" t="inlineStr">
@@ -2226,7 +2233,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 25 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
+Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
       <c r="H14" s="49" t="inlineStr">
@@ -2282,7 +2289,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 20 min: 1) SkiErg 15 cal 2) 25 wall balls 3) 8 burpee broad jumps 4) row 15 cal</t>
+Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
       <c r="H15" s="49" t="inlineStr">
@@ -2386,7 +2393,7 @@
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
 Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
+Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
         </is>
       </c>
       <c r="H17" s="49" t="inlineStr">
@@ -2602,7 +2609,7 @@
         <is>
           <t>Pull ups 2 x 5, press 2 x 5.
 Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 10 cal 2) 15 wall balls 3) row 10 cal 4) rest</t>
+Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
         </is>
       </c>
       <c r="H21" s="49" t="inlineStr">
@@ -2996,6 +3003,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="39">
       <c r="A30" s="41" t="inlineStr">
         <is>
@@ -6162,6 +6170,7 @@
       </c>
       <c r="G10" s="73" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="39">
       <c r="A12" s="45" t="inlineStr">
         <is>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -702,7 +702,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="39">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -802,7 +801,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="39">
       <c r="A12" s="47" t="inlineStr">
         <is>
@@ -824,7 +822,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="39">
       <c r="A16" s="47" t="inlineStr">
         <is>
@@ -1066,8 +1063,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="39">
       <c r="A29" s="47" t="inlineStr">
         <is>
@@ -1264,7 +1259,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38" ht="15" customHeight="1" s="39">
       <c r="A38" s="47" t="inlineStr">
         <is>
@@ -1371,7 +1365,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48" ht="15" customHeight="1" s="39">
       <c r="A48" s="47" t="inlineStr">
         <is>
@@ -1852,7 +1845,7 @@
       </c>
       <c r="E7" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
         </is>
       </c>
       <c r="F7" s="49" t="inlineStr">
@@ -1870,7 +1863,7 @@
       </c>
       <c r="H7" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 75%: 4 x (1 km + stations 1 to 4 at half volume)</t>
+          <t>Half sim, 75%, half volume, all 8 stations in race order: 8 x (500 m run + station at half volume)</t>
         </is>
       </c>
       <c r="I7" s="49" t="inlineStr">
@@ -1882,7 +1875,11 @@
         <v>11</v>
       </c>
       <c r="K7" s="58" t="n"/>
-      <c r="L7" s="59" t="n"/>
+      <c r="L7" s="59" t="inlineStr">
+        <is>
+          <t>First time through all 8 stations in race order (half volume)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="68.65000000000001" customHeight="1" s="39">
       <c r="A8" s="56" t="n">
@@ -1904,7 +1901,7 @@
       </c>
       <c r="E8" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
         </is>
       </c>
       <c r="F8" s="49" t="inlineStr">
@@ -2012,7 +2009,7 @@
       </c>
       <c r="E10" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (4 rounds, shorter: full sim Saturday): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
@@ -2030,7 +2027,7 @@
       </c>
       <c r="H10" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 80%: 4 x (1 km + stations 1 to 4 full volume)</t>
+          <t>FULL SIM at 85%: all 8, record splits</t>
         </is>
       </c>
       <c r="I10" s="49" t="inlineStr">
@@ -2042,7 +2039,11 @@
         <v>12</v>
       </c>
       <c r="K10" s="58" t="n"/>
-      <c r="L10" s="59" t="n"/>
+      <c r="L10" s="59" t="inlineStr">
+        <is>
+          <t>First full sim (moved up from week 19 for Nashville). Full sim again in week 19</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="68.65000000000001" customHeight="1" s="39">
       <c r="A11" s="60" t="n">
@@ -2082,7 +2083,7 @@
       </c>
       <c r="H11" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 80%: 4 x (1 km + stations 5 to 8 full volume)</t>
+          <t>Half sim, 75%, half volume: 4 x (500 m run + stations 5 to 8 at half volume). Sharpener before Nashville</t>
         </is>
       </c>
       <c r="I11" s="49" t="inlineStr">
@@ -2134,7 +2135,7 @@
       </c>
       <c r="H12" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 80%: 4 x (1 km + stations 1 to 4 full volume)</t>
+          <t>HYROX Nashville option (Dec 10 or 11, then this Saturday is rest). Else half sim, 80%: 4 x (1 km + stations 1 to 4 full volume)</t>
         </is>
       </c>
       <c r="I12" s="49" t="inlineStr">
@@ -2146,7 +2147,11 @@
         <v>14</v>
       </c>
       <c r="K12" s="58" t="n"/>
-      <c r="L12" s="59" t="n"/>
+      <c r="L12" s="59" t="inlineStr">
+        <is>
+          <t>If racing Nashville: Mon at about 80% loads, Tue 20 min easy, no hockey, the race replaces Fri and Sat</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="57.45" customHeight="1" s="39">
       <c r="A13" s="60" t="n">
@@ -6170,7 +6175,6 @@
       </c>
       <c r="G10" s="73" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="39">
       <c r="A12" s="45" t="inlineStr">
         <is>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1464,11 +1464,7 @@
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="39">
-      <c r="A62" s="42" t="inlineStr">
-        <is>
-          <t>• Optional tune up: HSQ half HYROX finale, Delson, Oct 17 to 18 2026 (week 3). Good baseline, not a target.</t>
-        </is>
-      </c>
+      <c r="A62" s="42" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1707,7 +1703,7 @@
       </c>
       <c r="H4" s="49" t="inlineStr">
         <is>
-          <t>Tune up option: HSQ Delson Oct 17 to 18. Else half sim stations 1 to 4, half volume, 75%</t>
+          <t>Half sim stations 1 to 4, half volume, 75%</t>
         </is>
       </c>
       <c r="I4" s="49" t="inlineStr">
@@ -3008,7 +3004,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="39">
       <c r="A30" s="41" t="inlineStr">
         <is>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E6" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F6" s="49" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E7" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F7" s="49" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E8" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F8" s="49" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E10" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (4 rounds, shorter: full sim Saturday): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (4 rounds, shorter: full sim Saturday): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E11" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F11" s="49" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E12" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F12" s="49" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E14" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F14" s="49" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E15" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m race weight 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F15" s="49" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E16" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min, race weights: 1) sled push 25 m 2) sandbag lunges 25 m 3) farmers 100 m 4) sled pull 25 m above race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F16" s="49" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="E18" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min, race weights: 1) sled push 25 m 2) sandbag lunges 25 m 3) farmers 100 m 4) sled pull 25 m above race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F18" s="49" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E19" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min, race weights: 1) sled push 25 m 2) sandbag lunges 25 m 3) farmers 100 m 4) sled pull 25 m above race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F19" s="49" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E20" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (shorter: full sim Saturday), race weights: 1) sled push 25 m 2) sandbag lunges 25 m 3) farmers 100 m 4) sled pull 25 m above race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F20" s="49" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="E22" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (shorter: full sim Saturday), race weights: 1) sled push 25 m 2) sandbag lunges 25 m 3) farmers 100 m 4) sled pull 25 m above race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F22" s="49" t="inlineStr">

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I1" s="48" t="inlineStr">
         <is>
-          <t>SUN: optional easy run</t>
+          <t>SUN: easy run</t>
         </is>
       </c>
       <c r="J1" s="48" t="inlineStr">
@@ -1708,11 +1708,11 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J4" s="49" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K4" s="58" t="n"/>
       <c r="L4" s="59" t="n"/>
@@ -1760,11 +1760,11 @@
       </c>
       <c r="I5" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J5" s="49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K5" s="58" t="n"/>
       <c r="L5" s="59" t="n"/>
@@ -1812,11 +1812,11 @@
       </c>
       <c r="I6" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J6" s="49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K6" s="58" t="n"/>
       <c r="L6" s="59" t="n"/>
@@ -1864,11 +1864,11 @@
       </c>
       <c r="I7" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J7" s="49" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K7" s="58" t="n"/>
       <c r="L7" s="59" t="inlineStr">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="I8" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J8" s="49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K8" s="58" t="n"/>
       <c r="L8" s="59" t="n"/>
@@ -1972,11 +1972,11 @@
       </c>
       <c r="I9" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J9" s="49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K9" s="58" t="n"/>
       <c r="L9" s="59" t="inlineStr">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="I10" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J10" s="49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K10" s="58" t="n"/>
       <c r="L10" s="59" t="inlineStr">
@@ -2084,11 +2084,11 @@
       </c>
       <c r="I11" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J11" s="49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K11" s="58" t="n"/>
       <c r="L11" s="59" t="n"/>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I12" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Optional: easy 20 to 30 min, only if fresh after the race</t>
         </is>
       </c>
       <c r="J12" s="49" t="n">
@@ -2192,11 +2192,11 @@
       </c>
       <c r="I13" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J13" s="49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K13" s="58" t="n"/>
       <c r="L13" s="59" t="n"/>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="I14" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J14" s="49" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K14" s="58" t="n"/>
       <c r="L14" s="59" t="inlineStr">
@@ -2300,11 +2300,11 @@
       </c>
       <c r="I15" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J15" s="49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K15" s="58" t="n"/>
       <c r="L15" s="59" t="n"/>
@@ -2352,11 +2352,11 @@
       </c>
       <c r="I16" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J16" s="49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K16" s="58" t="n"/>
       <c r="L16" s="59" t="n"/>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="I17" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J17" s="49" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K17" s="58" t="n"/>
       <c r="L17" s="59" t="inlineStr">
@@ -2460,11 +2460,11 @@
       </c>
       <c r="I18" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J18" s="49" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K18" s="58" t="n"/>
       <c r="L18" s="59" t="n"/>
@@ -2512,11 +2512,11 @@
       </c>
       <c r="I19" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J19" s="49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K19" s="58" t="n"/>
       <c r="L19" s="59" t="n"/>
@@ -2564,11 +2564,11 @@
       </c>
       <c r="I20" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J20" s="49" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K20" s="58" t="n"/>
       <c r="L20" s="59" t="inlineStr">
@@ -2620,11 +2620,11 @@
       </c>
       <c r="I21" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J21" s="49" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K21" s="58" t="n"/>
       <c r="L21" s="59" t="inlineStr">
@@ -2676,11 +2676,11 @@
       </c>
       <c r="I22" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J22" s="49" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K22" s="58" t="n"/>
       <c r="L22" s="59" t="n"/>
@@ -2728,11 +2728,11 @@
       </c>
       <c r="I23" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J23" s="49" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K23" s="58" t="n"/>
       <c r="L23" s="59" t="n"/>
@@ -2780,11 +2780,11 @@
       </c>
       <c r="I24" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J24" s="49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K24" s="58" t="n"/>
       <c r="L24" s="59" t="n"/>
@@ -2832,11 +2832,11 @@
       </c>
       <c r="I25" s="49" t="inlineStr">
         <is>
-          <t>Optional: 30 min easy, only if fresh</t>
+          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
         </is>
       </c>
       <c r="J25" s="49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K25" s="58" t="n"/>
       <c r="L25" s="59" t="inlineStr">
@@ -2888,11 +2888,11 @@
       </c>
       <c r="I26" s="49" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Easy run 30 min, conversational pace (taper)</t>
         </is>
       </c>
       <c r="J26" s="49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K26" s="58" t="n"/>
       <c r="L26" s="59" t="n"/>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1708,7 +1708,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J4" s="49" t="n">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="I5" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J5" s="49" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I6" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J6" s="49" t="n">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="I7" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J7" s="49" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="I8" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J8" s="49" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="I9" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J9" s="49" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="I10" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J10" s="49" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I11" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J11" s="49" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I12" s="49" t="inlineStr">
         <is>
-          <t>Optional: easy 20 to 30 min, only if fresh after the race</t>
+          <t>Optional: easy 20 to 30 min in zone 2, only if fresh after the race</t>
         </is>
       </c>
       <c r="J12" s="49" t="n">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="I13" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J13" s="49" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="I14" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J14" s="49" t="n">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="I15" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J15" s="49" t="n">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I16" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J16" s="49" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="I17" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J17" s="49" t="n">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I18" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J18" s="49" t="n">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="I19" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J19" s="49" t="n">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="I20" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J20" s="49" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="I21" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J21" s="49" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="I22" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J22" s="49" t="n">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I23" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J23" s="49" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="I24" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J24" s="49" t="n">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="I25" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 to 40 min, conversational pace (about 5 km)</t>
+          <t>Easy run 30 to 40 min in zone 2: 130 to 140 bpm, full sentences, slow is fine (about 5 km)</t>
         </is>
       </c>
       <c r="J25" s="49" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="I26" s="49" t="inlineStr">
         <is>
-          <t>Easy run 30 min, conversational pace (taper)</t>
+          <t>Easy run 30 min in zone 2: 130 to 140 bpm (taper)</t>
         </is>
       </c>
       <c r="J26" s="49" t="n">

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1424,7 +1424,7 @@
     <row r="56" ht="15" customHeight="1" s="39">
       <c r="A56" s="42" t="inlineStr">
         <is>
-          <t>• Weeks 4, 8, 12, 16, 20 are deloads: main lift 2 sets, secondary leg lift 2 x 8 light, EMOM 12 min light, about 30% less volume overall.</t>
+          <t>• Weeks 4, 8, 12, 16, 20 are deloads (changed Oct 19): lifts 3 sets at 80% of last load, EMOM 12 min at normal loads, Tuesday 4 intervals at normal pace, arms 3 sets each, Saturday sim at 75%. Volume drops, intensity stays.</t>
         </is>
       </c>
     </row>
@@ -1737,25 +1737,25 @@
       </c>
       <c r="E5" s="49" t="inlineStr">
         <is>
-          <t>Main lift 2 x 5 light. Hack squat 2 x 8 light. EMOM 12 min light (3 rounds): 1) sled push 20 m 2) 10 lunges/leg 3) farmers 50 m 4) rest</t>
+          <t>Trap bar DL 3 x 5 @ 80%. Hack squat 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 20 m 2) 10 lunges/leg bodyweight 3) farmers carry 50 m, 2 x 24 kg 4) rest</t>
         </is>
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>4 x 400 m easy
-Then arms block A, 2 sets each: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+          <t>4 x 600 m, 90 s rest
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G5" s="49" t="inlineStr">
         <is>
-          <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
+          <t>Weighted pull ups 3 x 5 @ 80%, DB bench 3 x 8 @ 80%.
+Then arms block B: Face pulls 3x15, cable crunch 3x10
+Finisher: EMOM 12 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H5" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 70%, half volume, stations 1 to 4</t>
+          <t>Half sim, 75%, half volume, stations 1 to 4</t>
         </is>
       </c>
       <c r="I5" s="49" t="inlineStr">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="J5" s="49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="58" t="n"/>
       <c r="L5" s="59" t="n"/>
@@ -1949,25 +1949,25 @@
       </c>
       <c r="E9" s="49" t="inlineStr">
         <is>
-          <t>Main lift 2 x 5 light. Hack squat 2 x 8 light. EMOM 12 min light (3 rounds): 1) sled push 20 m 2) 10 lunges/leg 3) farmers 50 m 4) rest</t>
+          <t>Trap bar DL 3 x 5 @ 80%. Hack squat 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>4 x 400 m easy
-Then arms block A, 2 sets each: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+          <t>4 x 1 km @ 10k pace, 2 min rest
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G9" s="49" t="inlineStr">
         <is>
-          <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
+          <t>Weighted pull ups 3 x 5 @ 80%, DB bench 3 x 8 @ 80%.
+Then arms block B: Face pulls 3x15, cable crunch 3x10
+Finisher: EMOM 12 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
       <c r="H9" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 70%, half volume, stations 5 to 8</t>
+          <t>Half sim, 75%, half volume, stations 5 to 8</t>
         </is>
       </c>
       <c r="I9" s="49" t="inlineStr">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="J9" s="49" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K9" s="58" t="n"/>
       <c r="L9" s="59" t="inlineStr">
@@ -2169,25 +2169,25 @@
       </c>
       <c r="E13" s="49" t="inlineStr">
         <is>
-          <t>Main lift 2 x 5 light. RDL 2 x 8 light. EMOM 12 min light (3 rounds): 1) sled push 20 m 2) 10 lunges/leg 3) farmers 50 m 4) rest</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>5 x 1 km easy
-Then arms block A, 2 sets each: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+          <t>4 x 1 km @ race pace, 2 min rest
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G13" s="49" t="inlineStr">
         <is>
-          <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
+          <t>Weighted pull ups 3 x 5 @ 80%, OHP 3 x 5 @ 80%.
+Then arms block B: Face pulls 3x15, cable crunch 3x10
+Finisher: EMOM 12 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
       <c r="H13" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 70%, half volume, stations 5 to 8</t>
+          <t>Half sim, 75%, half volume, stations 5 to 8</t>
         </is>
       </c>
       <c r="I13" s="49" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="E17" s="49" t="inlineStr">
         <is>
-          <t>Main lift 2 x 5 light. RDL 2 x 8 light. EMOM 12 min light (3 rounds): 1) sled push 20 m 2) 10 lunges/leg 3) farmers 50 m 4) rest</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>5 x 1 km easy
-Then arms block A, 2 sets each: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+          <t>4 x 1 km @ race pace, 90 s rest
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G17" s="49" t="inlineStr">
         <is>
-          <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
+          <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
+Then arms block B: Face pulls 3x15, cable crunch 3x10
+Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H17" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 70%, stations 1 to 4 full volume</t>
+          <t>Half sim, 75%, stations 1 to 4 full volume</t>
         </is>
       </c>
       <c r="I17" s="49" t="inlineStr">
@@ -2597,25 +2597,25 @@
       </c>
       <c r="E21" s="49" t="inlineStr">
         <is>
-          <t>Main lift 2 x 5 light. RDL 2 x 8 light. EMOM 12 min light (3 rounds): 1) sled push 20 m 2) 10 lunges/leg 3) farmers 50 m 4) rest</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>5 x 1 km easy
-Then arms block A, 2 sets each: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+          <t>4 x 1 km @ race pace, 90 s rest
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G21" s="49" t="inlineStr">
         <is>
-          <t>Pull ups 2 x 5, press 2 x 5.
-Then arms block B, 2 sets each: Face pulls 3x15, cable crunch 3x10
-Finisher: EMOM 12 min light: 1) SkiErg 125 m 2) 15 wall balls 3) row 125 m 4) rest</t>
+          <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
+Then arms block B: Face pulls 3x15, cable crunch 3x10
+Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H21" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 70%, stations 5 to 8 full volume</t>
+          <t>Half sim, 75%, stations 5 to 8 full volume</t>
         </is>
       </c>
       <c r="I21" s="49" t="inlineStr">
@@ -3004,6 +3004,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="39">
       <c r="A30" s="41" t="inlineStr">
         <is>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1749,7 +1749,7 @@
       <c r="G5" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, DB bench 3 x 8 @ 80%.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 12 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1795,13 +1795,13 @@
       <c r="F6" s="49" t="inlineStr">
         <is>
           <t>4 x 1 km @ 10k pace, 2 min rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G6" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1847,13 +1847,13 @@
       <c r="F7" s="49" t="inlineStr">
         <is>
           <t>5 x 1 km @ 10k pace, 2 min rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G7" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1903,13 +1903,13 @@
       <c r="F8" s="49" t="inlineStr">
         <is>
           <t>5 x 1 km @ 10k pace, 90 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G8" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1955,13 +1955,13 @@
       <c r="F9" s="49" t="inlineStr">
         <is>
           <t>4 x 1 km @ 10k pace, 2 min rest
-Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G9" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, DB bench 3 x 8 @ 80%.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 12 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -2011,13 +2011,13 @@
       <c r="F10" s="49" t="inlineStr">
         <is>
           <t>6 x 1 km @ race pace, 90 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G10" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2067,13 +2067,13 @@
       <c r="F11" s="49" t="inlineStr">
         <is>
           <t>6 x 1 km @ race pace, 75 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G11" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2119,13 +2119,13 @@
       <c r="F12" s="49" t="inlineStr">
         <is>
           <t>3 x 2 km @ race pace, 2 min rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G12" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2175,13 +2175,13 @@
       <c r="F13" s="49" t="inlineStr">
         <is>
           <t>4 x 1 km @ race pace, 2 min rest
-Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G13" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, OHP 3 x 5 @ 80%.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 12 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2227,13 +2227,13 @@
       <c r="F14" s="49" t="inlineStr">
         <is>
           <t>Holiday week: 5 km tempo
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G14" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2283,13 +2283,13 @@
       <c r="F15" s="49" t="inlineStr">
         <is>
           <t>8 x 1 km @ race pace, 60 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G15" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2335,13 +2335,13 @@
       <c r="F16" s="49" t="inlineStr">
         <is>
           <t>5 km tempo @ slightly faster than race pace
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G16" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2387,13 +2387,13 @@
       <c r="F17" s="49" t="inlineStr">
         <is>
           <t>4 x 1 km @ race pace, 90 s rest
-Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G17" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2443,13 +2443,13 @@
       <c r="F18" s="49" t="inlineStr">
         <is>
           <t>4 x 2 km @ race pace, 90 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G18" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2495,13 +2495,13 @@
       <c r="F19" s="49" t="inlineStr">
         <is>
           <t>6 km tempo
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G19" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2547,13 +2547,13 @@
       <c r="F20" s="49" t="inlineStr">
         <is>
           <t>Easy 5 km (full sim Saturday)
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G20" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2603,13 +2603,13 @@
       <c r="F21" s="49" t="inlineStr">
         <is>
           <t>4 x 1 km @ race pace, 90 s rest
-Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A, 3 sets each: Lateral raises 3x12-15, incline DB curls 3x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G21" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2659,13 +2659,13 @@
       <c r="F22" s="49" t="inlineStr">
         <is>
           <t>3 x 3 km @ race pace, 2 min rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G22" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2711,13 +2711,13 @@
       <c r="F23" s="49" t="inlineStr">
         <is>
           <t>6 x 1 km @ race pace, 60 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G23" s="49" t="inlineStr">
         <is>
           <t>Pull ups 3 x 5, press 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min at race effort: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2763,13 +2763,13 @@
       <c r="F24" s="49" t="inlineStr">
         <is>
           <t>8 x 1 km @ race pace, 45 s rest
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G24" s="49" t="inlineStr">
         <is>
           <t>Pull ups 3 x 5, press 3 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 20 min at race effort: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2815,13 +2815,13 @@
       <c r="F25" s="49" t="inlineStr">
         <is>
           <t>Easy 5 km (dress rehearsal Saturday)
-Then arms block A: Lateral raises 4x12-15, incline DB curls 3x10, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
+Then arms block A: Lateral raises 4x12-15, incline DB curls 4x8-12, overhead triceps ext 3x10, hanging leg raises 3x10-12</t>
         </is>
       </c>
       <c r="G25" s="49" t="inlineStr">
         <is>
           <t>Pull ups 2 x 5.
-Then arms block B: Face pulls 3x15, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
 Finisher: EMOM 8 min light: SkiErg, wall balls, row, rest</t>
         </is>
       </c>
@@ -3004,7 +3004,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="39">
       <c r="A30" s="41" t="inlineStr">
         <is>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E6" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F6" s="49" t="inlineStr">
@@ -1801,7 +1801,7 @@
       <c r="G6" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E7" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F7" s="49" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="G7" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E8" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
+          <t>Trap bar DL 3 x 5 heavy. Hack squat 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (4 rounds), moderate: 1) sled push 20 m (last round at race weight) 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F8" s="49" t="inlineStr">
@@ -1909,7 +1909,7 @@
       <c r="G8" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="E9" s="49" t="inlineStr">
         <is>
-          <t>Trap bar DL 3 x 5 @ 80%. Hack squat 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
+          <t>Trap bar DL 3 x 5 @ 80%. Hack squat 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 20 m 2) 10 lunges/leg 10 kg 3) farmers carry 50 m, 2 x 28 kg (above race weight, grip) 4) rest</t>
         </is>
       </c>
       <c r="F9" s="49" t="inlineStr">
@@ -1961,7 +1961,7 @@
       <c r="G9" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, DB bench 3 x 8 @ 80%.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 12 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E10" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (4 rounds, shorter: full sim Saturday): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (4 rounds, shorter: full sim Saturday): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F10" s="49" t="inlineStr">
@@ -2017,7 +2017,7 @@
       <c r="G10" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E11" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F11" s="49" t="inlineStr">
@@ -2073,7 +2073,7 @@
       <c r="G11" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E12" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F12" s="49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       <c r="G12" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="E13" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F13" s="49" t="inlineStr">
@@ -2181,7 +2181,7 @@
       <c r="G13" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, OHP 3 x 5 @ 80%.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 12 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E14" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F14" s="49" t="inlineStr">
@@ -2233,7 +2233,7 @@
       <c r="G14" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E15" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 20 min (5 rounds): 1) sled push 25 m race weight 2) sandbag lunges 20 m, 20 kg 3) farmers 60 m, 2 x 32 kg (above race weight, grip) 4) sled pull 12.5 m race weight</t>
         </is>
       </c>
       <c r="F15" s="49" t="inlineStr">
@@ -2289,7 +2289,7 @@
       <c r="G15" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E16" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F16" s="49" t="inlineStr">
@@ -2341,7 +2341,7 @@
       <c r="G16" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="E17" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F17" s="49" t="inlineStr">
@@ -2393,7 +2393,7 @@
       <c r="G17" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="E18" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F18" s="49" t="inlineStr">
@@ -2449,7 +2449,7 @@
       <c r="G18" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E19" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F19" s="49" t="inlineStr">
@@ -2501,7 +2501,7 @@
       <c r="G19" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="E20" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F20" s="49" t="inlineStr">
@@ -2553,7 +2553,7 @@
       <c r="G20" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="E21" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F21" s="49" t="inlineStr">
@@ -2609,7 +2609,7 @@
       <c r="G21" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="E22" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F22" s="49" t="inlineStr">
@@ -2665,7 +2665,7 @@
       <c r="G22" s="49" t="inlineStr">
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="E23" s="49" t="inlineStr">
         <is>
-          <t>Squat 3 x 3. EMOM 20 min at race weight and race effort: 1) sled push 25 m 2) lunges 25 m 3) farmers 100 m 4) sled pull 25 m</t>
+          <t>Squat 3 x 3. Cable crunch 3x10. EMOM 20 min at race weight and race effort: 1) sled push 25 m 2) lunges 25 m 3) farmers 100 m 4) sled pull 25 m</t>
         </is>
       </c>
       <c r="F23" s="49" t="inlineStr">
@@ -2717,7 +2717,7 @@
       <c r="G23" s="49" t="inlineStr">
         <is>
           <t>Pull ups 3 x 5, press 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min at race effort: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E24" s="49" t="inlineStr">
         <is>
-          <t>Squat 3 x 3. EMOM 20 min at race weight and race effort: 1) sled push 25 m 2) lunges 25 m 3) farmers 100 m 4) sled pull 25 m</t>
+          <t>Squat 3 x 3. Cable crunch 3x10. EMOM 20 min at race weight and race effort: 1) sled push 25 m 2) lunges 25 m 3) farmers 100 m 4) sled pull 25 m</t>
         </is>
       </c>
       <c r="F24" s="49" t="inlineStr">
@@ -2769,7 +2769,7 @@
       <c r="G24" s="49" t="inlineStr">
         <is>
           <t>Pull ups 3 x 5, press 3 x 5.
-Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12, cable crunch 3x10
+Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
 Finisher: EMOM 20 min at race effort: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1543,7 +1543,7 @@
       </c>
       <c r="J1" s="48" t="inlineStr">
         <is>
-          <t>Run km target</t>
+          <t>Run km target (planned runs only, no warm ups)</t>
         </is>
       </c>
       <c r="K1" s="48" t="inlineStr">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="J2" s="49" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="K2" s="58" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="J3" s="49" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="K3" s="58" t="n"/>
       <c r="L3" s="59" t="n"/>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="J4" s="49" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K4" s="58" t="n"/>
       <c r="L4" s="59" t="n"/>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="J5" s="49" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="K5" s="58" t="n"/>
       <c r="L5" s="59" t="n"/>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="J6" s="49" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K6" s="58" t="n"/>
       <c r="L6" s="59" t="n"/>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="J7" s="49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K7" s="58" t="n"/>
       <c r="L7" s="59" t="inlineStr">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="J8" s="49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K8" s="58" t="n"/>
       <c r="L8" s="59" t="n"/>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="J9" s="49" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K9" s="58" t="n"/>
       <c r="L9" s="59" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="J10" s="49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K10" s="58" t="n"/>
       <c r="L10" s="59" t="inlineStr">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="J11" s="49" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K11" s="58" t="n"/>
       <c r="L11" s="59" t="n"/>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="J12" s="49" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K12" s="58" t="n"/>
       <c r="L12" s="59" t="inlineStr">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="J13" s="49" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K13" s="58" t="n"/>
       <c r="L13" s="59" t="n"/>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="J14" s="49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K14" s="58" t="n"/>
       <c r="L14" s="59" t="inlineStr">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="J15" s="49" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K15" s="58" t="n"/>
       <c r="L15" s="59" t="n"/>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="J16" s="49" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K16" s="58" t="n"/>
       <c r="L16" s="59" t="n"/>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="J17" s="49" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K17" s="58" t="n"/>
       <c r="L17" s="59" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="J18" s="49" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K18" s="58" t="n"/>
       <c r="L18" s="59" t="n"/>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="J19" s="49" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K19" s="58" t="n"/>
       <c r="L19" s="59" t="n"/>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="J20" s="49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K20" s="58" t="n"/>
       <c r="L20" s="59" t="inlineStr">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="J21" s="49" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K21" s="58" t="n"/>
       <c r="L21" s="59" t="inlineStr">
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="J22" s="49" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K22" s="58" t="n"/>
       <c r="L22" s="59" t="n"/>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="J23" s="49" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K23" s="58" t="n"/>
       <c r="L23" s="59" t="n"/>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="J24" s="49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K24" s="58" t="n"/>
       <c r="L24" s="59" t="n"/>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="J25" s="49" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K25" s="58" t="n"/>
       <c r="L25" s="59" t="inlineStr">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="J26" s="49" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K26" s="58" t="n"/>
       <c r="L26" s="59" t="n"/>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="J27" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K27" s="58" t="n"/>
       <c r="L27" s="59" t="inlineStr">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="J28" s="49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K28" s="58" t="n"/>
       <c r="L28" s="59" t="inlineStr">

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -685,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="38" min="1" max="1"/>
@@ -702,6 +702,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="39">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -801,6 +802,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="39">
       <c r="A12" s="47" t="inlineStr">
         <is>
@@ -822,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="39">
       <c r="A16" s="47" t="inlineStr">
         <is>
@@ -1063,6 +1066,8 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="39">
       <c r="A29" s="47" t="inlineStr">
         <is>
@@ -1259,6 +1264,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="15" customHeight="1" s="39">
       <c r="A38" s="47" t="inlineStr">
         <is>
@@ -1365,6 +1371,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48" ht="15" customHeight="1" s="39">
       <c r="A48" s="47" t="inlineStr">
         <is>
@@ -1465,6 +1472,13 @@
     </row>
     <row r="62" ht="15" customHeight="1" s="39">
       <c r="A62" s="42" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Fred only (Oct 31): wall ball technique 2 x 10 on Fridays weeks 6 to 21; weeks 15 to 21 EMOM wall balls with a 9 kg (20 lb) ball and Monday sandbag lunges at 25 kg. Will and Grady keep the base plan in the app.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1854,6 +1868,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1910,6 +1925,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, DB bench 3 x 8.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 16 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -1962,6 +1978,7 @@
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, DB bench 3 x 8 @ 80%.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 12 min: 1) SkiErg 150 m 2) 15 wall balls 3) row 150 m 4) rest</t>
         </is>
       </c>
@@ -2018,6 +2035,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2074,6 +2092,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2126,6 +2145,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2182,6 +2202,7 @@
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, OHP 3 x 5 @ 80%.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 12 min: 1) SkiErg 200 m 2) 20 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2234,6 +2255,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2290,6 +2312,7 @@
         <is>
           <t>Weighted pull ups 3 x 5, OHP 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
+Wall ball technique 2 x 10.
 Finisher: EMOM 20 min: 1) SkiErg 200 m 2) 25 wall balls 3) 8 burpee broad jumps 4) row 200 m</t>
         </is>
       </c>
@@ -2329,7 +2352,7 @@
       </c>
       <c r="E16" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F16" s="49" t="inlineStr">
@@ -2342,7 +2365,8 @@
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H16" s="49" t="inlineStr">
@@ -2381,7 +2405,7 @@
       </c>
       <c r="E17" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F17" s="49" t="inlineStr">
@@ -2394,7 +2418,8 @@
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H17" s="49" t="inlineStr">
@@ -2437,7 +2462,7 @@
       </c>
       <c r="E18" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F18" s="49" t="inlineStr">
@@ -2450,7 +2475,8 @@
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H18" s="49" t="inlineStr">
@@ -2489,7 +2515,7 @@
       </c>
       <c r="E19" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 24 min: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F19" s="49" t="inlineStr">
@@ -2502,7 +2528,8 @@
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 24 min: 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H19" s="49" t="inlineStr">
@@ -2541,7 +2568,7 @@
       </c>
       <c r="E20" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F20" s="49" t="inlineStr">
@@ -2554,7 +2581,8 @@
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H20" s="49" t="inlineStr">
@@ -2597,7 +2625,7 @@
       </c>
       <c r="E21" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5 @ 80%. RDL 3 x 8 @ 80%. Cable crunch 3x10. EMOM 12 min (3 rounds), normal loads: 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F21" s="49" t="inlineStr">
@@ -2610,7 +2638,8 @@
         <is>
           <t>Weighted pull ups 3 x 5 @ 80%, bench 3 x 5 @ 80%.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 12 min: 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H21" s="49" t="inlineStr">
@@ -2653,7 +2682,7 @@
       </c>
       <c r="E22" s="49" t="inlineStr">
         <is>
-          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 20 kg 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
+          <t>Back squat 3 x 5. RDL 3 x 8 @ RPE 7. Cable crunch 3x10. EMOM 16 min (shorter: full sim Saturday): 1) sled push 15 m at 110% race weight 2) sandbag lunges 25 m, 25 kg (above race weight) 3) farmers 100 m, 2 x 30 kg (above race weight, grip) 4) sled pull 15 m at 110% race weight</t>
         </is>
       </c>
       <c r="F22" s="49" t="inlineStr">
@@ -2666,7 +2695,8 @@
         <is>
           <t>Weighted pull ups 3 x 5, bench 3 x 5.
 Then arms block B: Face pulls 3x15, Bayesian cable curls 3x10-12, hammer curls 3x10-12
-Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 3) 10 burpee broad jumps 4) row 250 m</t>
+Wall ball technique 2 x 10.
+Finisher: EMOM 16 min (shorter: full sim Saturday): 1) SkiErg 250 m 2) 25 wall balls 9 kg (20 lb) 3) 10 burpee broad jumps 4) row 250 m</t>
         </is>
       </c>
       <c r="H22" s="49" t="inlineStr">

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -702,7 +702,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="39">
       <c r="A3" s="41" t="inlineStr">
         <is>
@@ -802,7 +801,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="39">
       <c r="A12" s="47" t="inlineStr">
         <is>
@@ -824,7 +822,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="39">
       <c r="A16" s="47" t="inlineStr">
         <is>
@@ -1066,8 +1063,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="39">
       <c r="A29" s="47" t="inlineStr">
         <is>
@@ -1264,7 +1259,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38" ht="15" customHeight="1" s="39">
       <c r="A38" s="47" t="inlineStr">
         <is>
@@ -1371,7 +1365,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48" ht="15" customHeight="1" s="39">
       <c r="A48" s="47" t="inlineStr">
         <is>
@@ -1474,9 +1467,9 @@
       <c r="A62" s="42" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Fred only (Oct 31): wall ball technique 2 x 10 on Fridays weeks 6 to 21; weeks 15 to 21 EMOM wall balls with a 9 kg (20 lb) ball and Monday sandbag lunges at 25 kg. Will and Grady keep the base plan in the app.</t>
+      <c r="A63" s="38" t="inlineStr">
+        <is>
+          <t>Oct 31: Fridays weeks 6 to 21 add wall ball technique 2 x 10 (Fred only). Weeks 15 to 21 for everyone: EMOM wall balls with a 9 kg (20 lb) ball and Monday sandbag lunges at 25 kg.</t>
         </is>
       </c>
     </row>

--- a/plan/HYROX_Brisbane_2027_Plan.xlsx
+++ b/plan/HYROX_Brisbane_2027_Plan.xlsx
@@ -1867,7 +1867,7 @@
       </c>
       <c r="H7" s="49" t="inlineStr">
         <is>
-          <t>Half sim, 75%, half volume, all 8 stations in race order: 8 x (500 m run + station at half volume)</t>
+          <t>Half sim, 75%, half volume, all 8 stations in race order: 8 x (1 km run + station at half volume)</t>
         </is>
       </c>
       <c r="I7" s="49" t="inlineStr">
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="J7" s="49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K7" s="58" t="n"/>
       <c r="L7" s="59" t="inlineStr">
